--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B2" t="n">
-        <v>58052</v>
+        <v>100451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R2" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ylva Hanell, Nina Marliden</t>
+          <t>Nina Marliden, Ylva Hanell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>58052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R3" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ylva Hanell, Nina Marliden</t>
+          <t>Nina Marliden, Ylva Hanell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B2" t="n">
-        <v>100451</v>
+        <v>58052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R2" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +788,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nina Marliden, Ylva Hanell</t>
+          <t>Ylva Hanell, Nina Marliden</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B3" t="n">
-        <v>58052</v>
+        <v>100451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R3" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nina Marliden, Ylva Hanell</t>
+          <t>Ylva Hanell, Nina Marliden</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122173417</v>
       </c>
       <c r="B2" t="n">
-        <v>58052</v>
+        <v>58057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>122173458</v>
       </c>
       <c r="B3" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>100468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R2" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B3" t="n">
-        <v>100463</v>
+        <v>58057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R3" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B2" t="n">
-        <v>100468</v>
+        <v>58057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>103044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R2" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>100477</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +806,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R3" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>100490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>222498</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R2" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B3" t="n">
-        <v>100477</v>
+        <v>58061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,29 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R3" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122173458</v>
       </c>
       <c r="B2" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 48911-2023 artfynd.xlsx
+++ b/artfynd/A 48911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122173458</v>
+        <v>122173417</v>
       </c>
       <c r="B2" t="n">
-        <v>100503</v>
+        <v>58061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533618</v>
+        <v>533596</v>
       </c>
       <c r="R2" t="n">
-        <v>6364384</v>
+        <v>6364401</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122173417</v>
+        <v>122173458</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>100503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Järnforsen, Kalmar, Sm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533596</v>
+        <v>533618</v>
       </c>
       <c r="R3" t="n">
-        <v>6364401</v>
+        <v>6364384</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
